--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
@@ -935,43 +935,43 @@
     <t>214</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>R$ 9.681,64</t>
+    <t>37</t>
+  </si>
+  <si>
+    <t>R$ 9.689,76</t>
   </si>
   <si>
     <t>101.4</t>
   </si>
   <si>
-    <t>70.6</t>
-  </si>
-  <si>
-    <t>6.40</t>
-  </si>
-  <si>
-    <t>21.7</t>
-  </si>
-  <si>
-    <t>8.6</t>
-  </si>
-  <si>
-    <t>5.8</t>
-  </si>
-  <si>
-    <t>30.5%</t>
-  </si>
-  <si>
-    <t>18.3%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
+    <t>70.7</t>
+  </si>
+  <si>
+    <t>6.49</t>
+  </si>
+  <si>
+    <t>21.9</t>
+  </si>
+  <si>
+    <t>8.7</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>30.1%</t>
+  </si>
+  <si>
+    <t>18.6%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>3.6%</t>
+    <t>3.5%</t>
   </si>
   <si>
     <t>1.1%</t>
@@ -980,46 +980,46 @@
     <t>6.2%</t>
   </si>
   <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
-  </si>
-  <si>
-    <t>2726.0</t>
-  </si>
-  <si>
-    <t>2206.0</t>
-  </si>
-  <si>
-    <t>163.0</t>
-  </si>
-  <si>
-    <t>23.0</t>
-  </si>
-  <si>
-    <t>430.0</t>
-  </si>
-  <si>
-    <t>134.0</t>
-  </si>
-  <si>
-    <t>22.0</t>
-  </si>
-  <si>
-    <t>749.0</t>
-  </si>
-  <si>
-    <t>271.0</t>
-  </si>
-  <si>
-    <t>908.0</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>49.0</t>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>7.7%</t>
+  </si>
+  <si>
+    <t>2835.0</t>
+  </si>
+  <si>
+    <t>2306.0</t>
+  </si>
+  <si>
+    <t>169.0</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>438.0</t>
+  </si>
+  <si>
+    <t>137.0</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
+    <t>762.0</t>
+  </si>
+  <si>
+    <t>289.0</t>
+  </si>
+  <si>
+    <t>955.0</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>61.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3239,7 +3239,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3269,35 +3269,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>15512</v>
+      </c>
+      <c r="N13" s="6">
+        <v>162</v>
+      </c>
+      <c r="O13" s="6">
+        <v>130</v>
+      </c>
+      <c r="P13" s="7">
+        <v>14.067272727272726</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>29.772307692307692</v>
+      </c>
+      <c r="R13" s="8">
+        <v>7.4516669230769228</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.13846153846153847</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.23846153846153847</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.023076923076923078</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>32</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>31</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.092307692307692313</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>12</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -10478,7 +10536,9 @@
       <c r="N62" s="6">
         <v>86</v>
       </c>
-      <c r="O62" s="6"/>
+      <c r="O62" s="6">
+        <v>54</v>
+      </c>
       <c r="P62" s="7">
         <v>3.1877390804597701</v>
       </c>
@@ -10488,31 +10548,75 @@
       <c r="R62" s="8">
         <v>7.0955134615384612</v>
       </c>
-      <c r="S62" s="8"/>
+      <c r="S62" s="8">
+        <v>7</v>
+      </c>
       <c r="T62" s="9">
         <v>0.40740740740740738</v>
       </c>
-      <c r="U62" s="9"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="9"/>
-      <c r="AC62" s="9"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="6"/>
-      <c r="AF62" s="6"/>
-      <c r="AG62" s="6"/>
-      <c r="AH62" s="6"/>
-      <c r="AI62" s="6"/>
-      <c r="AJ62" s="6"/>
-      <c r="AK62" s="6"/>
-      <c r="AL62" s="6"/>
-      <c r="AM62" s="6"/>
-      <c r="AN62" s="9"/>
-      <c r="AO62" s="6"/>
+      <c r="U62" s="9">
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="V62" s="9">
+        <v>0</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9">
+        <v>0.092592592592592587</v>
+      </c>
+      <c r="Y62" s="9">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="Z62" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="AA62" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="AB62" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="AC62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AK62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP62" s="4">
         <v>58</v>
       </c>
@@ -14418,7 +14522,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>51</v>
@@ -14448,35 +14552,93 @@
         <v>58</v>
       </c>
       <c r="L90" s="4"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="6"/>
-      <c r="O90" s="6"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="8"/>
-      <c r="R90" s="8"/>
-      <c r="S90" s="8"/>
-      <c r="T90" s="9"/>
-      <c r="U90" s="9"/>
-      <c r="V90" s="9"/>
-      <c r="W90" s="9"/>
-      <c r="X90" s="9"/>
-      <c r="Y90" s="9"/>
-      <c r="Z90" s="9"/>
-      <c r="AA90" s="9"/>
-      <c r="AB90" s="9"/>
-      <c r="AC90" s="9"/>
-      <c r="AD90" s="6"/>
-      <c r="AE90" s="6"/>
-      <c r="AF90" s="6"/>
-      <c r="AG90" s="6"/>
-      <c r="AH90" s="6"/>
-      <c r="AI90" s="6"/>
-      <c r="AJ90" s="6"/>
-      <c r="AK90" s="6"/>
-      <c r="AL90" s="6"/>
-      <c r="AM90" s="6"/>
-      <c r="AN90" s="9"/>
-      <c r="AO90" s="6"/>
+      <c r="M90" s="5">
+        <v>8103.5299999999997</v>
+      </c>
+      <c r="N90" s="6">
+        <v>79</v>
+      </c>
+      <c r="O90" s="6">
+        <v>62</v>
+      </c>
+      <c r="P90" s="7">
+        <v>14.025406097560976</v>
+      </c>
+      <c r="Q90" s="8">
+        <v>42.885483870967747</v>
+      </c>
+      <c r="R90" s="8">
+        <v>21.194624193548389</v>
+      </c>
+      <c r="S90" s="8">
+        <v>7</v>
+      </c>
+      <c r="T90" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="U90" s="9">
+        <v>0.66129032258064513</v>
+      </c>
+      <c r="V90" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="W90" s="9">
+        <v>0</v>
+      </c>
+      <c r="X90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="9">
+        <v>0.17741935483870969</v>
+      </c>
+      <c r="AC90" s="9">
+        <v>0.45161290322580644</v>
+      </c>
+      <c r="AD90" s="6">
+        <v>43</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>41</v>
+      </c>
+      <c r="AF90" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="6">
+        <v>11</v>
+      </c>
+      <c r="AM90" s="6">
+        <v>28</v>
+      </c>
+      <c r="AN90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO90" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP90" s="4">
         <v>58</v>
       </c>
@@ -16176,7 +16338,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16206,35 +16368,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>6858.21</v>
+      </c>
+      <c r="N102" s="6">
+        <v>77</v>
+      </c>
+      <c r="O102" s="6">
+        <v>55</v>
+      </c>
+      <c r="P102" s="7">
+        <v>6.7989716049382709</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>18.919090909090908</v>
+      </c>
+      <c r="R102" s="8">
+        <v>6.9260416666666664</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.29090909090909089</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.054545454544999997</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.036363636363636362</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.16363636363636364</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>22</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>11</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>9</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
@@ -935,37 +935,37 @@
     <t>214</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>R$ 9.689,76</t>
-  </si>
-  <si>
-    <t>101.4</t>
-  </si>
-  <si>
-    <t>70.7</t>
-  </si>
-  <si>
-    <t>6.49</t>
-  </si>
-  <si>
-    <t>21.9</t>
-  </si>
-  <si>
-    <t>8.7</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>30.1%</t>
-  </si>
-  <si>
-    <t>18.6%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 9.764,04</t>
+  </si>
+  <si>
+    <t>101.5</t>
+  </si>
+  <si>
+    <t>71.2</t>
+  </si>
+  <si>
+    <t>6.51</t>
+  </si>
+  <si>
+    <t>22.0</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>29.7%</t>
+  </si>
+  <si>
+    <t>18.3%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -977,43 +977,43 @@
     <t>1.1%</t>
   </si>
   <si>
-    <t>6.2%</t>
+    <t>6.0%</t>
   </si>
   <si>
     <t>2.3%</t>
   </si>
   <si>
-    <t>7.7%</t>
-  </si>
-  <si>
-    <t>2835.0</t>
-  </si>
-  <si>
-    <t>2306.0</t>
-  </si>
-  <si>
-    <t>169.0</t>
+    <t>7.6%</t>
+  </si>
+  <si>
+    <t>2880.0</t>
+  </si>
+  <si>
+    <t>2347.0</t>
+  </si>
+  <si>
+    <t>170.0</t>
   </si>
   <si>
     <t>26.0</t>
   </si>
   <si>
-    <t>438.0</t>
+    <t>448.0</t>
   </si>
   <si>
     <t>137.0</t>
   </si>
   <si>
-    <t>24.0</t>
-  </si>
-  <si>
-    <t>762.0</t>
-  </si>
-  <si>
-    <t>289.0</t>
-  </si>
-  <si>
-    <t>955.0</t>
+    <t>25.0</t>
+  </si>
+  <si>
+    <t>769.0</t>
+  </si>
+  <si>
+    <t>297.0</t>
+  </si>
+  <si>
+    <t>973.0</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -2206,7 +2206,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2236,35 +2236,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>19283.93</v>
+      </c>
+      <c r="N6" s="6">
+        <v>171</v>
+      </c>
+      <c r="O6" s="6">
+        <v>149</v>
+      </c>
+      <c r="P6" s="7">
+        <v>12.456395348837209</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>22.911968456375838</v>
+      </c>
+      <c r="R6" s="8">
+        <v>3.1299547297297297</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.26174496644295303</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.046979865771812082</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0.0067114093959731542</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.0067114093959731542</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.020134228187919462</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0.013422818791946308</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -5528,7 +5586,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5558,35 +5616,93 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="M28" s="5">
+        <v>12907.67</v>
+      </c>
+      <c r="N28" s="6">
+        <v>121</v>
+      </c>
+      <c r="O28" s="6">
+        <v>68</v>
+      </c>
+      <c r="P28" s="7">
+        <v>4.1789256198347102</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>22.190049253731345</v>
+      </c>
+      <c r="R28" s="8">
+        <v>11.017910447761194</v>
+      </c>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.28358208955223879</v>
+      </c>
+      <c r="U28" s="9">
+        <v>0.14705882352941177</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0.014705882352941176</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>8</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -6969,7 +7085,7 @@
         <v>9.4473968750000008</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>0.41176470588235292</v>
@@ -11537,7 +11653,7 @@
         <v>19647</v>
       </c>
       <c r="B69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C69" s="4">
         <v>51</v>
@@ -11565,8 +11681,12 @@
         <v>58</v>
       </c>
       <c r="L69" s="4"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="6"/>
+      <c r="M69" s="5">
+        <v>0</v>
+      </c>
+      <c r="N69" s="6">
+        <v>0</v>
+      </c>
       <c r="O69" s="6"/>
       <c r="P69" s="7"/>
       <c r="Q69" s="8"/>
@@ -12510,7 +12630,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12538,35 +12658,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>10466.200000000001</v>
+      </c>
+      <c r="N76" s="6">
+        <v>129</v>
+      </c>
+      <c r="O76" s="6">
+        <v>62</v>
+      </c>
+      <c r="P76" s="7">
+        <v>3.8230282442748091</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>35.817204838709678</v>
+      </c>
+      <c r="R76" s="8">
+        <v>23.786723728813559</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.25806451612903225</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0.016129032258064516</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>21</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -24626,7 +24804,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -24656,35 +24834,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>9472.3899999999994</v>
+      </c>
+      <c r="N158" s="6">
+        <v>89</v>
+      </c>
+      <c r="O158" s="6">
+        <v>75</v>
+      </c>
+      <c r="P158" s="7">
+        <v>10.61666629213483</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>31.972222666666671</v>
+      </c>
+      <c r="R158" s="8">
+        <v>13.746</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -30171,7 +30407,9 @@
       <c r="N195" s="6">
         <v>104</v>
       </c>
-      <c r="O195" s="6"/>
+      <c r="O195" s="6">
+        <v>77</v>
+      </c>
       <c r="P195" s="7">
         <v>6.1039215686274515</v>
       </c>
@@ -30181,31 +30419,75 @@
       <c r="R195" s="8">
         <v>12.612120779220779</v>
       </c>
-      <c r="S195" s="8"/>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
       <c r="T195" s="9">
         <v>0.051948051948051951</v>
       </c>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="U195" s="9">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
@@ -935,22 +935,22 @@
     <t>214</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 9.764,04</t>
-  </si>
-  <si>
-    <t>101.5</t>
-  </si>
-  <si>
-    <t>71.2</t>
-  </si>
-  <si>
-    <t>6.51</t>
-  </si>
-  <si>
-    <t>22.0</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 9.778,97</t>
+  </si>
+  <si>
+    <t>101.7</t>
+  </si>
+  <si>
+    <t>71.5</t>
+  </si>
+  <si>
+    <t>6.54</t>
+  </si>
+  <si>
+    <t>22.1</t>
   </si>
   <si>
     <t>8.8</t>
@@ -959,10 +959,10 @@
     <t>6.1</t>
   </si>
   <si>
-    <t>29.7%</t>
-  </si>
-  <si>
-    <t>18.3%</t>
+    <t>29.5%</t>
+  </si>
+  <si>
+    <t>18.1%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -977,28 +977,28 @@
     <t>1.1%</t>
   </si>
   <si>
-    <t>6.0%</t>
+    <t>5.9%</t>
   </si>
   <si>
     <t>2.3%</t>
   </si>
   <si>
-    <t>7.6%</t>
-  </si>
-  <si>
-    <t>2880.0</t>
-  </si>
-  <si>
-    <t>2347.0</t>
-  </si>
-  <si>
-    <t>170.0</t>
+    <t>7.5%</t>
+  </si>
+  <si>
+    <t>2891.0</t>
+  </si>
+  <si>
+    <t>2358.0</t>
+  </si>
+  <si>
+    <t>175.0</t>
   </si>
   <si>
     <t>26.0</t>
   </si>
   <si>
-    <t>448.0</t>
+    <t>449.0</t>
   </si>
   <si>
     <t>137.0</t>
@@ -1007,13 +1007,13 @@
     <t>25.0</t>
   </si>
   <si>
-    <t>769.0</t>
+    <t>772.0</t>
   </si>
   <si>
     <t>297.0</t>
   </si>
   <si>
-    <t>973.0</t>
+    <t>975.0</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -6782,7 +6782,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6812,35 +6812,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>10427.73</v>
+      </c>
+      <c r="N36" s="6">
+        <v>129</v>
+      </c>
+      <c r="O36" s="6">
+        <v>108</v>
+      </c>
+      <c r="P36" s="7">
+        <v>10.762132352941178</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>38.06898148148148</v>
+      </c>
+      <c r="R36" s="8">
+        <v>20.381775700934579</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0.0092592592592592587</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.0092592592592592587</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.0092592592592592587</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7664,7 +7722,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7694,35 +7752,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>11818.24</v>
+      </c>
+      <c r="N42" s="6">
+        <v>122</v>
+      </c>
+      <c r="O42" s="6">
+        <v>88</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.0912353448275862</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>21.254980459770113</v>
+      </c>
+      <c r="R42" s="8">
+        <v>8.1312264367816098</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.25287356321839083</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
@@ -932,94 +932,97 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 9.778,97</t>
-  </si>
-  <si>
-    <t>101.7</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 9.774,73</t>
+  </si>
+  <si>
+    <t>101.8</t>
   </si>
   <si>
     <t>71.5</t>
   </si>
   <si>
-    <t>6.54</t>
-  </si>
-  <si>
-    <t>22.1</t>
+    <t>6.72</t>
+  </si>
+  <si>
+    <t>22.2</t>
   </si>
   <si>
     <t>8.8</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>29.5%</t>
-  </si>
-  <si>
-    <t>18.1%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>29.0%</t>
+  </si>
+  <si>
+    <t>19.1%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
-  </si>
-  <si>
-    <t>2891.0</t>
-  </si>
-  <si>
-    <t>2358.0</t>
-  </si>
-  <si>
-    <t>175.0</t>
+    <t>3.4%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>8.1%</t>
+  </si>
+  <si>
+    <t>3135.0</t>
+  </si>
+  <si>
+    <t>2544.0</t>
+  </si>
+  <si>
+    <t>180.0</t>
   </si>
   <si>
     <t>26.0</t>
   </si>
   <si>
-    <t>449.0</t>
-  </si>
-  <si>
-    <t>137.0</t>
+    <t>454.0</t>
+  </si>
+  <si>
+    <t>139.0</t>
   </si>
   <si>
     <t>25.0</t>
   </si>
   <si>
-    <t>772.0</t>
-  </si>
-  <si>
-    <t>297.0</t>
-  </si>
-  <si>
-    <t>975.0</t>
+    <t>870.0</t>
+  </si>
+  <si>
+    <t>320.0</t>
+  </si>
+  <si>
+    <t>1083.0</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>61.0</t>
+    <t>64.0</t>
   </si>
   <si>
     <t>1</t>
@@ -6526,7 +6529,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6556,35 +6559,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>11391.1</v>
+      </c>
+      <c r="N34" s="6">
+        <v>151</v>
+      </c>
+      <c r="O34" s="6">
+        <v>115</v>
+      </c>
+      <c r="P34" s="7">
+        <v>33.23388543046358</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>42.091739130434782</v>
+      </c>
+      <c r="R34" s="8">
+        <v>0.7670030303030303</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.060869565217391307</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.16521739130434782</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0.41739130434782606</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>142</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>92</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>75</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>19</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>48</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -18678,33 +18739,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>39</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.17948717948717949</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -22433,7 +22540,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22463,35 +22570,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>7385.9399999999996</v>
+      </c>
+      <c r="N141" s="6">
+        <v>76</v>
+      </c>
+      <c r="O141" s="6">
+        <v>49</v>
+      </c>
+      <c r="P141" s="7">
+        <v>14.106798684210526</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>23.403402040816324</v>
+      </c>
+      <c r="R141" s="8">
+        <v>4.7698935483870972</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0.38775510204081631</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>21</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>21</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>19</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -33260,137 +33425,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>87</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.75862068965517238</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0.022988505747126436</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0.045977011494252873</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0.022988505747126436</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0.022988505747126436</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>73</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>66</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>58</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0.022988505747126436</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>2</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
-        <v>319</v>
-      </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="Z217" s="11">
+        <v>320</v>
+      </c>
+      <c t="s" r="AA217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>336</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c t="s" r="AO217" s="11">
         <v>337</v>
       </c>
-      <c t="s" r="AY216" s="11">
-        <v>337</v>
-      </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
+        <v>338</v>
+      </c>
+      <c t="s" r="AY217" s="11">
+        <v>338</v>
+      </c>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
@@ -938,10 +938,10 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 9.774,73</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 9.776,95</t>
   </si>
   <si>
     <t>101.8</t>
@@ -950,10 +950,10 @@
     <t>71.5</t>
   </si>
   <si>
-    <t>6.72</t>
-  </si>
-  <si>
-    <t>22.2</t>
+    <t>6.74</t>
+  </si>
+  <si>
+    <t>22.3</t>
   </si>
   <si>
     <t>8.8</t>
@@ -14780,7 +14780,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14808,14 +14808,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>10184.940000000001</v>
+      </c>
+      <c r="N89" s="6">
+        <v>86</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>10.260185555555555</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>28.549146153846152</v>
+      </c>
+      <c r="R89" s="8">
+        <v>10.743694594594595</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.12820512820512819</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -29142,7 +29154,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31850,7 +31862,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33429,7 +33441,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-02).xlsx
@@ -938,37 +938,37 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 9.776,95</t>
+    <t>R$ 9.646,64</t>
   </si>
   <si>
-    <t>101.8</t>
+    <t>100.4</t>
   </si>
   <si>
     <t>71.5</t>
   </si>
   <si>
-    <t>6.74</t>
+    <t>6.71</t>
   </si>
   <si>
-    <t>22.3</t>
+    <t>22.4</t>
   </si>
   <si>
-    <t>8.8</t>
+    <t>8.9</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>29.0%</t>
+    <t>29.1%</t>
   </si>
   <si>
-    <t>19.1%</t>
+    <t>18.9%</t>
   </si>
   <si>
-    <t>1.4%</t>
+    <t>1.3%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -986,22 +986,22 @@
     <t>2.4%</t>
   </si>
   <si>
-    <t>8.1%</t>
+    <t>8.0%</t>
   </si>
   <si>
-    <t>3135.0</t>
+    <t>3162.0</t>
   </si>
   <si>
-    <t>2544.0</t>
+    <t>2572.0</t>
   </si>
   <si>
-    <t>180.0</t>
+    <t>182.0</t>
   </si>
   <si>
-    <t>26.0</t>
+    <t>28.0</t>
   </si>
   <si>
-    <t>454.0</t>
+    <t>462.0</t>
   </si>
   <si>
     <t>139.0</t>
@@ -1010,13 +1010,13 @@
     <t>25.0</t>
   </si>
   <si>
-    <t>870.0</t>
+    <t>884.0</t>
   </si>
   <si>
-    <t>320.0</t>
+    <t>321.0</t>
   </si>
   <si>
-    <t>1083.0</t>
+    <t>1085.0</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -9190,7 +9190,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9220,14 +9220,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1128.4200000000001</v>
+      </c>
+      <c r="N51" s="6">
+        <v>13</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>4.9892857142857139</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>48.25</v>
+      </c>
+      <c r="R51" s="8">
+        <v>36.666649999999997</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10259,33 +10271,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>111</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.081081081081081086</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.018018018018018018</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0.0090090090090000005</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.027027027027027029</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0.0090090090090090089</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.0090090090090090089</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.018018018018018018</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -21998,7 +22056,7 @@
         <v>19787</v>
       </c>
       <c r="B137" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C137" s="4">
         <v>51</v>
@@ -22026,18 +22084,30 @@
         <v>58</v>
       </c>
       <c r="L137" s="4"/>
-      <c r="M137" s="5"/>
-      <c r="N137" s="6"/>
+      <c r="M137" s="5">
+        <v>3429.5599999999999</v>
+      </c>
+      <c r="N137" s="6">
+        <v>36</v>
+      </c>
       <c r="O137" s="6">
         <v>15</v>
       </c>
-      <c r="P137" s="7"/>
-      <c r="Q137" s="8"/>
-      <c r="R137" s="8"/>
+      <c r="P137" s="7">
+        <v>7.3773138888888887</v>
+      </c>
+      <c r="Q137" s="8">
+        <v>27.814446666666665</v>
+      </c>
+      <c r="R137" s="8">
+        <v>12.879999999999999</v>
+      </c>
       <c r="S137" s="8">
         <v>7</v>
       </c>
-      <c r="T137" s="9"/>
+      <c r="T137" s="9">
+        <v>0</v>
+      </c>
       <c r="U137" s="9">
         <v>0.13333333333333333</v>
       </c>
@@ -24116,7 +24186,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24146,35 +24216,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>8141.04</v>
+      </c>
+      <c r="N151" s="6">
+        <v>93</v>
+      </c>
+      <c r="O151" s="6">
+        <v>80</v>
+      </c>
+      <c r="P151" s="7">
+        <v>4.2614698924731185</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>13.526875</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.4160341772151899</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.6875</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -24998,7 +25126,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25028,35 +25156,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>8171.3299999999999</v>
+      </c>
+      <c r="N157" s="6">
+        <v>81</v>
+      </c>
+      <c r="O157" s="6">
+        <v>72</v>
+      </c>
+      <c r="P157" s="7">
+        <v>8.5993750000000002</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>19.010648611111108</v>
+      </c>
+      <c r="R157" s="8">
+        <v>4.1343920634920632</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.15277777777777779</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.18055555555555555</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>12</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -26138,7 +26324,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26168,35 +26354,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>5280.7799999999997</v>
+      </c>
+      <c r="N165" s="6">
+        <v>54</v>
+      </c>
+      <c r="O165" s="6">
+        <v>29</v>
+      </c>
+      <c r="P165" s="7">
+        <v>4.2629629629629626</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>12.217241379310344</v>
+      </c>
+      <c r="R165" s="8">
+        <v>1.0086206896551724</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.89655172413793105</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0.034482758619999998</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
@@ -26237,7 +26481,7 @@
         <v>19879</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>51</v>
@@ -26267,14 +26511,26 @@
         <v>58</v>
       </c>
       <c r="L166" s="4"/>
-      <c r="M166" s="5"/>
-      <c r="N166" s="6"/>
+      <c r="M166" s="5">
+        <v>7620.9499999999998</v>
+      </c>
+      <c r="N166" s="6">
+        <v>67</v>
+      </c>
       <c r="O166" s="6"/>
-      <c r="P166" s="7"/>
-      <c r="Q166" s="8"/>
-      <c r="R166" s="8"/>
+      <c r="P166" s="7">
+        <v>4.4007692307692308</v>
+      </c>
+      <c r="Q166" s="8">
+        <v>33.349493939393938</v>
+      </c>
+      <c r="R166" s="8">
+        <v>22.688021875</v>
+      </c>
       <c r="S166" s="8"/>
-      <c r="T166" s="9"/>
+      <c r="T166" s="9">
+        <v>0.090909090909090912</v>
+      </c>
       <c r="U166" s="9"/>
       <c r="V166" s="9"/>
       <c r="W166" s="9"/>
